--- a/meta_analysis/Dataset_data_curated_final.xlsx
+++ b/meta_analysis/Dataset_data_curated_final.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mbp16/Documents/Coding/HP407/data_processing/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mbp16/Documents/Coding/HP407/meta_analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{497599BB-D46A-724B-9FD1-436C241B428C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA7404B1-2D21-F741-810B-B05C1F881C37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7780" yWindow="2280" windowWidth="22780" windowHeight="17880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7780" yWindow="2280" windowWidth="22780" windowHeight="17880" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="caregiver_Burden" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="caregiver_Behaviour" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">caregiver_Behaviour!$A$1:$BH$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">caregiver_Behaviour!$A$1:$BH$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">caregiver_Burden!$A$1:$AR$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">caregiver_MentalHealth!$A$1:$BI$27</definedName>
   </definedNames>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
@@ -132,7 +132,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2658" uniqueCount="561">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2670" uniqueCount="561">
   <si>
     <t>Study Identifier</t>
   </si>
@@ -9936,6 +9936,9 @@
       <c r="AE12" s="1" t="s">
         <v>449</v>
       </c>
+      <c r="AF12" s="1" t="s">
+        <v>290</v>
+      </c>
       <c r="AG12" s="1" t="s">
         <v>176</v>
       </c>
@@ -9944,6 +9947,15 @@
       </c>
       <c r="AI12" s="1" t="s">
         <v>177</v>
+      </c>
+      <c r="AJ12" t="s">
+        <v>173</v>
+      </c>
+      <c r="AK12" t="s">
+        <v>174</v>
+      </c>
+      <c r="AL12" t="s">
+        <v>175</v>
       </c>
       <c r="AM12" s="1" t="s">
         <v>447</v>
@@ -10049,6 +10061,9 @@
       <c r="AE13" s="1" t="s">
         <v>449</v>
       </c>
+      <c r="AF13" s="1" t="s">
+        <v>290</v>
+      </c>
       <c r="AG13" s="1" t="s">
         <v>191</v>
       </c>
@@ -10057,6 +10072,15 @@
       </c>
       <c r="AI13" s="1" t="s">
         <v>192</v>
+      </c>
+      <c r="AJ13" t="s">
+        <v>189</v>
+      </c>
+      <c r="AK13" t="s">
+        <v>174</v>
+      </c>
+      <c r="AL13" t="s">
+        <v>190</v>
       </c>
       <c r="AM13" s="1" t="s">
         <v>447</v>
@@ -10816,6 +10840,9 @@
       <c r="AL20" t="s">
         <v>344</v>
       </c>
+      <c r="AM20" t="s">
+        <v>47</v>
+      </c>
       <c r="AO20" t="s">
         <v>356</v>
       </c>
@@ -10908,6 +10935,9 @@
       <c r="AL21" t="s">
         <v>359</v>
       </c>
+      <c r="AM21" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="22" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
@@ -11000,6 +11030,9 @@
       <c r="AL22" t="s">
         <v>404</v>
       </c>
+      <c r="AM22" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="23" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
@@ -11092,6 +11125,9 @@
       <c r="AL23" t="s">
         <v>418</v>
       </c>
+      <c r="AM23" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="24" spans="1:43" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
@@ -11785,372 +11821,372 @@
         <v>525</v>
       </c>
     </row>
-    <row r="32" spans="1:43" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="2" t="s">
+    <row r="32" spans="1:43" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="5" t="s">
         <v>491</v>
       </c>
-      <c r="B32" s="2">
+      <c r="B32" s="5">
         <v>2019</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="D32" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="F32" s="2" t="e" vm="2">
+      <c r="F32" s="5" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
-      <c r="G32" s="2" t="s">
+      <c r="G32" s="5" t="s">
         <v>492</v>
       </c>
-      <c r="H32" s="2" t="s">
+      <c r="H32" s="5" t="s">
         <v>493</v>
       </c>
-      <c r="I32" s="2" t="s">
+      <c r="I32" s="5" t="s">
         <v>494</v>
       </c>
-      <c r="J32" s="2" t="s">
+      <c r="J32" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="K32" s="2" t="s">
+      <c r="K32" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="L32" s="2" t="s">
+      <c r="L32" s="5" t="s">
         <v>490</v>
       </c>
-      <c r="M32" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="N32" s="2" t="s">
+      <c r="M32" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="N32" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="O32" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="P32" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q32" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="R32" s="2" t="s">
+      <c r="O32" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="P32" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q32" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="R32" s="5" t="s">
         <v>530</v>
       </c>
-      <c r="T32" s="2" t="s">
+      <c r="T32" s="5" t="s">
         <v>532</v>
       </c>
-      <c r="U32" s="4">
+      <c r="U32" s="11">
         <v>0.88</v>
       </c>
-      <c r="Z32" s="2" t="s">
+      <c r="Z32" s="5" t="s">
         <v>533</v>
       </c>
-      <c r="AC32" s="2" t="s">
+      <c r="AC32" s="5" t="s">
         <v>83</v>
       </c>
       <c r="AN32" s="5" t="s">
         <v>535</v>
       </c>
     </row>
-    <row r="33" spans="1:40" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="2" t="s">
+    <row r="33" spans="1:40" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="5" t="s">
         <v>491</v>
       </c>
-      <c r="B33" s="2">
+      <c r="B33" s="5">
         <v>2019</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D33" s="2" t="s">
+      <c r="D33" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="F33" s="2" t="e" vm="2">
+      <c r="F33" s="5" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
-      <c r="G33" s="2" t="s">
+      <c r="G33" s="5" t="s">
         <v>492</v>
       </c>
-      <c r="H33" s="2" t="s">
+      <c r="H33" s="5" t="s">
         <v>493</v>
       </c>
-      <c r="I33" s="2" t="s">
+      <c r="I33" s="5" t="s">
         <v>494</v>
       </c>
-      <c r="J33" s="2" t="s">
+      <c r="J33" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="K33" s="2" t="s">
+      <c r="K33" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="L33" s="2" t="s">
+      <c r="L33" s="5" t="s">
         <v>490</v>
       </c>
-      <c r="M33" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="N33" s="2" t="s">
+      <c r="M33" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="N33" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="O33" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="P33" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q33" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="R33" s="2" t="s">
+      <c r="O33" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="P33" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q33" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="R33" s="5" t="s">
         <v>529</v>
       </c>
-      <c r="T33" s="2" t="s">
+      <c r="T33" s="5" t="s">
         <v>531</v>
       </c>
-      <c r="U33" s="4">
+      <c r="U33" s="11">
         <v>0.72</v>
       </c>
-      <c r="Z33" s="2" t="s">
+      <c r="Z33" s="5" t="s">
         <v>534</v>
       </c>
-      <c r="AC33" s="2" t="s">
+      <c r="AC33" s="5" t="s">
         <v>83</v>
       </c>
       <c r="AN33" s="5" t="s">
         <v>535</v>
       </c>
     </row>
-    <row r="34" spans="1:40" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="2" t="s">
+    <row r="34" spans="1:40" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="5" t="s">
         <v>495</v>
       </c>
-      <c r="B34" s="2">
+      <c r="B34" s="5">
         <v>2019</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C34" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="D34" s="2" t="s">
+      <c r="D34" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="F34" s="2" t="e" vm="7">
+      <c r="F34" s="5" t="e" vm="7">
         <v>#VALUE!</v>
       </c>
-      <c r="G34" s="2" t="s">
+      <c r="G34" s="5" t="s">
         <v>537</v>
       </c>
-      <c r="H34" s="2" t="s">
+      <c r="H34" s="5" t="s">
         <v>497</v>
       </c>
-      <c r="I34" s="2" t="s">
+      <c r="I34" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="J34" s="2" t="s">
+      <c r="J34" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="K34" s="2" t="s">
+      <c r="K34" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="L34" s="2" t="s">
+      <c r="L34" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="M34" s="2" t="s">
+      <c r="M34" s="5" t="s">
         <v>490</v>
       </c>
-      <c r="N34" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="O34" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="P34" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q34" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="S34" s="3">
+      <c r="N34" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="O34" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="P34" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q34" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="S34" s="6">
         <v>0.71430000000000005</v>
       </c>
-      <c r="T34" s="2" t="s">
+      <c r="T34" s="5" t="s">
         <v>540</v>
       </c>
-      <c r="U34" s="3">
+      <c r="U34" s="6">
         <v>0.55359999999999998</v>
       </c>
-      <c r="Z34" s="2" t="s">
+      <c r="Z34" s="5" t="s">
         <v>538</v>
       </c>
-      <c r="AC34" s="2" t="s">
+      <c r="AC34" s="5" t="s">
         <v>83</v>
       </c>
       <c r="AN34" s="5" t="s">
         <v>535</v>
       </c>
     </row>
-    <row r="35" spans="1:40" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="2" t="s">
+    <row r="35" spans="1:40" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="5" t="s">
         <v>495</v>
       </c>
-      <c r="B35" s="2">
+      <c r="B35" s="5">
         <v>2019</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C35" s="5" t="s">
         <v>285</v>
       </c>
-      <c r="D35" s="2" t="s">
+      <c r="D35" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="F35" s="2" t="e" vm="7">
+      <c r="F35" s="5" t="e" vm="7">
         <v>#VALUE!</v>
       </c>
-      <c r="G35" s="2" t="s">
+      <c r="G35" s="5" t="s">
         <v>537</v>
       </c>
-      <c r="H35" s="2" t="s">
+      <c r="H35" s="5" t="s">
         <v>497</v>
       </c>
-      <c r="I35" s="2" t="s">
+      <c r="I35" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="J35" s="2" t="s">
+      <c r="J35" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="K35" s="2" t="s">
+      <c r="K35" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="L35" s="2" t="s">
+      <c r="L35" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="M35" s="2" t="s">
+      <c r="M35" s="5" t="s">
         <v>490</v>
       </c>
-      <c r="N35" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="O35" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="P35" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q35" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="S35" s="3">
+      <c r="N35" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="O35" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="P35" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q35" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="S35" s="6">
         <v>0.63390000000000002</v>
       </c>
-      <c r="T35" s="2" t="s">
+      <c r="T35" s="5" t="s">
         <v>541</v>
       </c>
-      <c r="U35" s="3">
+      <c r="U35" s="6">
         <v>0.69640000000000002</v>
       </c>
-      <c r="Z35" s="2" t="s">
+      <c r="Z35" s="5" t="s">
         <v>539</v>
       </c>
-      <c r="AC35" s="2" t="s">
+      <c r="AC35" s="5" t="s">
         <v>83</v>
       </c>
       <c r="AN35" s="5" t="s">
         <v>535</v>
       </c>
     </row>
-    <row r="36" spans="1:40" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="2" t="s">
+    <row r="36" spans="1:40" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="5" t="s">
         <v>496</v>
       </c>
-      <c r="B36" s="2">
+      <c r="B36" s="5">
         <v>2020</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="C36" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="D36" s="2" t="s">
+      <c r="D36" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="F36" s="2" t="e" vm="2">
+      <c r="F36" s="5" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
-      <c r="G36" s="2" t="s">
+      <c r="G36" s="5" t="s">
         <v>552</v>
       </c>
-      <c r="K36" s="2" t="s">
+      <c r="K36" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="L36" s="2" t="s">
+      <c r="L36" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="M36" s="2" t="s">
+      <c r="M36" s="5" t="s">
         <v>490</v>
       </c>
-      <c r="N36" s="2" t="s">
+      <c r="N36" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="O36" s="2" t="s">
+      <c r="O36" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="P36" s="2" t="s">
+      <c r="P36" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="Q36" s="2" t="s">
+      <c r="Q36" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="Z36" s="2" t="s">
+      <c r="Z36" s="5" t="s">
         <v>553</v>
       </c>
-      <c r="AC36" s="2" t="s">
+      <c r="AC36" s="5" t="s">
         <v>83</v>
       </c>
       <c r="AN36" s="5" t="s">
         <v>535</v>
       </c>
     </row>
-    <row r="37" spans="1:40" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="2" t="s">
+    <row r="37" spans="1:40" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="5" t="s">
         <v>496</v>
       </c>
-      <c r="B37" s="2">
+      <c r="B37" s="5">
         <v>2020</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="C37" s="5" t="s">
         <v>285</v>
       </c>
-      <c r="D37" s="2" t="s">
+      <c r="D37" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="F37" s="2" t="e" vm="2">
+      <c r="F37" s="5" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
-      <c r="G37" s="2" t="s">
+      <c r="G37" s="5" t="s">
         <v>552</v>
       </c>
-      <c r="K37" s="2" t="s">
+      <c r="K37" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="L37" s="2" t="s">
+      <c r="L37" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="M37" s="2" t="s">
+      <c r="M37" s="5" t="s">
         <v>490</v>
       </c>
-      <c r="N37" s="2" t="s">
+      <c r="N37" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="O37" s="2" t="s">
+      <c r="O37" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="P37" s="2" t="s">
+      <c r="P37" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="Q37" s="2" t="s">
+      <c r="Q37" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="Z37" s="2" t="s">
+      <c r="Z37" s="5" t="s">
         <v>554</v>
       </c>
-      <c r="AC37" s="2" t="s">
+      <c r="AC37" s="5" t="s">
         <v>83</v>
       </c>
       <c r="AN37" s="5" t="s">
@@ -18543,7 +18579,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH19" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
+  <autoFilter ref="A1:BH33" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/meta_analysis/Dataset_data_curated_final.xlsx
+++ b/meta_analysis/Dataset_data_curated_final.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mbp16/Documents/Coding/HP407/meta_analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA7404B1-2D21-F741-810B-B05C1F881C37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95CD0ED7-980D-5944-9ED9-1E48090BFC50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7780" yWindow="2280" windowWidth="22780" windowHeight="17880" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="600" yWindow="9180" windowWidth="33940" windowHeight="17880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="caregiver_Burden" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="caregiver_Behaviour" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">caregiver_Behaviour!$A$1:$BH$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">caregiver_Behaviour!$A$1:$BH$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">caregiver_Burden!$A$1:$AR$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">caregiver_MentalHealth!$A$1:$BI$27</definedName>
   </definedNames>
@@ -132,7 +132,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2670" uniqueCount="561">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2664" uniqueCount="563">
   <si>
     <t>Study Identifier</t>
   </si>
@@ -1892,6 +1892,14 @@
   </si>
   <si>
     <t>The authors used SE rather than SD. I converted SE to SD, assuming N = 157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"1．2．1．1方案制定及社区护士培训研究者在文献 查阅基础上形成初稿，经4位精神科及老年科护理领 域专家论证后，最终形成《社区失智老人居家照顾者照 护技能培训方案》及《失智症照顾者手册》。社区护士 失智症管理培训以学习讲座形式进行，由4位失智症 护理及老年护理领域专家授课，内容主要包括：①家庭 访视的方法和技巧；②认识失智症；③失智症的家庭护 理；④失智症日常康复训练；⑤照顾者自我照顾及社区 资源支持；⑥常规护理实践指导；⑦失智症日常生活照 顾实践指导等。采用体验式学习法，以情景模拟体验、 案例分析分享、小组讨论交流等多种方式进行，由授课 专家对培训护士进行理论及实践操作考核。共计5次 课程，每次3 h～4 h。 1．2．1．2人员分配及家庭访视 根据社区医护人员 课程培训结果，对培训合格的社区护士进行人员分配 及职责划分，每名护士负责3例～4例失智老人居家 照顾者的家庭访视，每2周进行1次集中讨论，讨论本 组内失智老人及其照顾者的现况并实时更新记录，如 遇不能解决的照顾问题，及时向专家求助。家庭访视 每周1次，每次1．5 h～2．0 h，具体工作可进行个体化 调整，注重理论学习与实际生活的联系，所有内容都要
+针对照顾者家庭的实际情况由社区护士进行一对一指 导。首次家庭访视时主动进行自我介绍，获得照顾者 的信任和许可后，发放《失智症照顾者手册》及用以预 防失智老人走失的“黄手环”，评估失智老人的基本情 况(病人病情、日常生活能力等)及照顾者需求(疾病知 识、协助病人日常活动、环境安全设施设置等)等问题 并记录，结合手册进行失智症疾病基础知识的指导，使 照顾者意识到失智症并非是正常老化所造成的，是需 要治疗和护理的，让照顾者对失智症有一定的了解。 第2次结合“日常生活照顾指导”主题，按照家庭访视 常规流程进行，以手册为基础对照顾者进行饮食、口腔 卫生、排泄、洗澡穿衣及睡眠休息等内容的指导，如何 为失智老人提供营养丰富的三餐，运用定时如厕等方 法避免失智老人弄脏衣裤等。第3次进行“安全护理” 及“康复技能”指导，如何预防与应对异常行为、定向力 及记忆力训练等内容，引导失智老人浏览老照片、讲述 老故事以延缓记忆衰退等。第4次进行“照顾者自我 照顾”及“社区医疗资源利用”指导，引导照顾者接纳病 人，进行自我心理调适；合理安排时间，多参与健身及 娱乐活动以丰富生活，同时减轻照顾压力；多与家庭成 员交流，勇于表达自己的难处，接受外界的帮助，建立 有效的家庭支持系统；合理接纳和利用来自社区医疗 机构及心理援助组织的相关医疗支持；了解日间照护中心、“护老者之家”、喘息服务等政府养老服务资源并 学会根据自己的实际情况做出最佳的医疗服务决策。 在进行理论学习的同时，根据被访家庭的具体情况，由 社区护士为其提供个性化的支持和指导，注重与照顾 者的交流，利用倾听、共情、肢体接触等方式为照顾者 提供心理及情感支持，允许照顾者通过抱怨、哭泣等方 式进行不良情绪的发泄；将社区养老服务机构的宣传 资料发给照顾者，详细介绍社区资源的使用条件及方 法，同照顾者一起根据失智老人的健康状况及家庭条 件选择最佳的养老服务；陪照顾者检视家庭环境，排除 存在跌倒风险的居家陈设，减少青团、糕团等易诱发噎 食的食物，引导照顾者积极对待照顾活动，将所学知识 真正融人实际生活。 1．2．1．3 电话随访 家庭访视结束后，每周1次电话 随访照顾者，通过与照顾者电话沟通了解仍未解决的 问题，并予以指导，根据情况可以安排再次进行人户。 第2个月开始每两周进行1次电话随访，直至干预 结束。 "
+</t>
+  </si>
+  <si>
+    <t>The original dataset only provides change from baseline data. The raw data is  updated from the original paper.</t>
   </si>
 </sst>
 </file>
@@ -1958,7 +1966,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -1971,6 +1979,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -8921,13 +8932,43 @@
         <v>434</v>
       </c>
       <c r="AF2" t="s">
-        <v>437</v>
+        <v>290</v>
+      </c>
+      <c r="AG2">
+        <v>21.7</v>
+      </c>
+      <c r="AH2">
+        <v>40</v>
+      </c>
+      <c r="AI2">
+        <v>13.1</v>
+      </c>
+      <c r="AJ2">
+        <v>21.5</v>
       </c>
       <c r="AK2">
+        <v>32</v>
+      </c>
+      <c r="AL2">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>447</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>562</v>
+      </c>
+      <c r="AO2">
+        <v>21.4</v>
+      </c>
+      <c r="AP2">
         <v>26</v>
       </c>
-      <c r="AM2" t="s">
-        <v>433</v>
+      <c r="AQ2">
+        <v>16.2</v>
+      </c>
+      <c r="AR2" t="s">
+        <v>447</v>
       </c>
     </row>
     <row r="3" spans="1:44" x14ac:dyDescent="0.2">
@@ -9010,19 +9051,43 @@
         <v>434</v>
       </c>
       <c r="AF3" t="s">
-        <v>437</v>
+        <v>290</v>
+      </c>
+      <c r="AG3">
+        <v>24.8</v>
+      </c>
+      <c r="AH3">
+        <v>41</v>
+      </c>
+      <c r="AI3">
+        <v>14.9</v>
       </c>
       <c r="AJ3">
-        <v>-3.29</v>
+        <v>19.5</v>
       </c>
       <c r="AK3">
+        <v>34</v>
+      </c>
+      <c r="AL3">
+        <v>13</v>
+      </c>
+      <c r="AM3" t="s">
+        <v>447</v>
+      </c>
+      <c r="AN3" t="s">
+        <v>562</v>
+      </c>
+      <c r="AO3">
+        <v>19</v>
+      </c>
+      <c r="AP3">
         <v>33</v>
       </c>
-      <c r="AL3">
-        <v>1.7450000000000001</v>
-      </c>
-      <c r="AM3" t="s">
-        <v>433</v>
+      <c r="AQ3">
+        <v>13</v>
+      </c>
+      <c r="AR3" t="s">
+        <v>447</v>
       </c>
     </row>
     <row r="4" spans="1:44" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -9936,9 +10001,6 @@
       <c r="AE12" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="AF12" s="1" t="s">
-        <v>290</v>
-      </c>
       <c r="AG12" s="1" t="s">
         <v>176</v>
       </c>
@@ -9948,13 +10010,13 @@
       <c r="AI12" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="AJ12" t="s">
+      <c r="AJ12" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="AK12" t="s">
+      <c r="AK12" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="AL12" t="s">
+      <c r="AL12" s="1" t="s">
         <v>175</v>
       </c>
       <c r="AM12" s="1" t="s">
@@ -9962,15 +10024,6 @@
       </c>
       <c r="AN12" s="1" t="s">
         <v>471</v>
-      </c>
-      <c r="AO12" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="AP12" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="AQ12" s="1" t="s">
-        <v>175</v>
       </c>
       <c r="AR12" s="1" t="s">
         <v>447</v>
@@ -10061,9 +10114,6 @@
       <c r="AE13" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="AF13" s="1" t="s">
-        <v>290</v>
-      </c>
       <c r="AG13" s="1" t="s">
         <v>191</v>
       </c>
@@ -10073,13 +10123,13 @@
       <c r="AI13" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="AJ13" t="s">
+      <c r="AJ13" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="AK13" t="s">
+      <c r="AK13" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="AL13" t="s">
+      <c r="AL13" s="1" t="s">
         <v>190</v>
       </c>
       <c r="AM13" s="1" t="s">
@@ -10087,15 +10137,6 @@
       </c>
       <c r="AN13" s="1" t="s">
         <v>471</v>
-      </c>
-      <c r="AO13" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="AP13" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="AQ13" s="1" t="s">
-        <v>190</v>
       </c>
       <c r="AR13" s="1" t="s">
         <v>447</v>
@@ -10840,9 +10881,6 @@
       <c r="AL20" t="s">
         <v>344</v>
       </c>
-      <c r="AM20" t="s">
-        <v>47</v>
-      </c>
       <c r="AO20" t="s">
         <v>356</v>
       </c>
@@ -10935,11 +10973,8 @@
       <c r="AL21" t="s">
         <v>359</v>
       </c>
-      <c r="AM21" t="s">
-        <v>47</v>
-      </c>
     </row>
-    <row r="22" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:43" ht="14" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>396</v>
       </c>
@@ -11003,8 +11038,8 @@
       <c r="Z22" t="s">
         <v>402</v>
       </c>
-      <c r="AA22" t="s">
-        <v>403</v>
+      <c r="AA22" s="12" t="s">
+        <v>561</v>
       </c>
       <c r="AC22" t="s">
         <v>57</v>
@@ -11021,17 +11056,23 @@
       <c r="AG22" t="s">
         <v>407</v>
       </c>
+      <c r="AH22">
+        <v>78</v>
+      </c>
       <c r="AI22" t="s">
         <v>406</v>
       </c>
       <c r="AJ22" t="s">
         <v>405</v>
       </c>
+      <c r="AK22">
+        <v>78</v>
+      </c>
       <c r="AL22" t="s">
         <v>404</v>
       </c>
       <c r="AM22" t="s">
-        <v>47</v>
+        <v>433</v>
       </c>
     </row>
     <row r="23" spans="1:43" x14ac:dyDescent="0.2">
@@ -11116,17 +11157,23 @@
       <c r="AG23" t="s">
         <v>421</v>
       </c>
+      <c r="AH23">
+        <v>78</v>
+      </c>
       <c r="AI23" t="s">
         <v>420</v>
       </c>
       <c r="AJ23" t="s">
         <v>419</v>
       </c>
+      <c r="AK23">
+        <v>78</v>
+      </c>
       <c r="AL23" t="s">
         <v>418</v>
       </c>
       <c r="AM23" t="s">
-        <v>47</v>
+        <v>433</v>
       </c>
     </row>
     <row r="24" spans="1:43" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -11821,372 +11868,372 @@
         <v>525</v>
       </c>
     </row>
-    <row r="32" spans="1:43" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="5" t="s">
+    <row r="32" spans="1:43" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="2" t="s">
         <v>491</v>
       </c>
-      <c r="B32" s="5">
+      <c r="B32" s="2">
         <v>2019</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="C32" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D32" s="5" t="s">
+      <c r="D32" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="F32" s="5" t="e" vm="2">
+      <c r="F32" s="2" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
-      <c r="G32" s="5" t="s">
+      <c r="G32" s="2" t="s">
         <v>492</v>
       </c>
-      <c r="H32" s="5" t="s">
+      <c r="H32" s="2" t="s">
         <v>493</v>
       </c>
-      <c r="I32" s="5" t="s">
+      <c r="I32" s="2" t="s">
         <v>494</v>
       </c>
-      <c r="J32" s="5" t="s">
+      <c r="J32" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="K32" s="5" t="s">
+      <c r="K32" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="L32" s="5" t="s">
+      <c r="L32" s="2" t="s">
         <v>490</v>
       </c>
-      <c r="M32" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="N32" s="5" t="s">
+      <c r="M32" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="N32" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="O32" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="P32" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q32" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="R32" s="5" t="s">
+      <c r="O32" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="P32" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q32" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="R32" s="2" t="s">
         <v>530</v>
       </c>
-      <c r="T32" s="5" t="s">
+      <c r="T32" s="2" t="s">
         <v>532</v>
       </c>
-      <c r="U32" s="11">
+      <c r="U32" s="4">
         <v>0.88</v>
       </c>
-      <c r="Z32" s="5" t="s">
+      <c r="Z32" s="2" t="s">
         <v>533</v>
       </c>
-      <c r="AC32" s="5" t="s">
+      <c r="AC32" s="2" t="s">
         <v>83</v>
       </c>
       <c r="AN32" s="5" t="s">
         <v>535</v>
       </c>
     </row>
-    <row r="33" spans="1:40" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="5" t="s">
+    <row r="33" spans="1:40" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="2" t="s">
         <v>491</v>
       </c>
-      <c r="B33" s="5">
+      <c r="B33" s="2">
         <v>2019</v>
       </c>
-      <c r="C33" s="5" t="s">
+      <c r="C33" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D33" s="5" t="s">
+      <c r="D33" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="F33" s="5" t="e" vm="2">
+      <c r="F33" s="2" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
-      <c r="G33" s="5" t="s">
+      <c r="G33" s="2" t="s">
         <v>492</v>
       </c>
-      <c r="H33" s="5" t="s">
+      <c r="H33" s="2" t="s">
         <v>493</v>
       </c>
-      <c r="I33" s="5" t="s">
+      <c r="I33" s="2" t="s">
         <v>494</v>
       </c>
-      <c r="J33" s="5" t="s">
+      <c r="J33" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="K33" s="5" t="s">
+      <c r="K33" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="L33" s="5" t="s">
+      <c r="L33" s="2" t="s">
         <v>490</v>
       </c>
-      <c r="M33" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="N33" s="5" t="s">
+      <c r="M33" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="N33" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="O33" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="P33" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q33" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="R33" s="5" t="s">
+      <c r="O33" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="P33" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q33" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="R33" s="2" t="s">
         <v>529</v>
       </c>
-      <c r="T33" s="5" t="s">
+      <c r="T33" s="2" t="s">
         <v>531</v>
       </c>
-      <c r="U33" s="11">
+      <c r="U33" s="4">
         <v>0.72</v>
       </c>
-      <c r="Z33" s="5" t="s">
+      <c r="Z33" s="2" t="s">
         <v>534</v>
       </c>
-      <c r="AC33" s="5" t="s">
+      <c r="AC33" s="2" t="s">
         <v>83</v>
       </c>
       <c r="AN33" s="5" t="s">
         <v>535</v>
       </c>
     </row>
-    <row r="34" spans="1:40" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="5" t="s">
+    <row r="34" spans="1:40" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="2" t="s">
         <v>495</v>
       </c>
-      <c r="B34" s="5">
+      <c r="B34" s="2">
         <v>2019</v>
       </c>
-      <c r="C34" s="5" t="s">
+      <c r="C34" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D34" s="5" t="s">
+      <c r="D34" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="F34" s="5" t="e" vm="7">
+      <c r="F34" s="2" t="e" vm="7">
         <v>#VALUE!</v>
       </c>
-      <c r="G34" s="5" t="s">
+      <c r="G34" s="2" t="s">
         <v>537</v>
       </c>
-      <c r="H34" s="5" t="s">
+      <c r="H34" s="2" t="s">
         <v>497</v>
       </c>
-      <c r="I34" s="5" t="s">
+      <c r="I34" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="J34" s="5" t="s">
+      <c r="J34" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="K34" s="5" t="s">
+      <c r="K34" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="L34" s="5" t="s">
+      <c r="L34" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="M34" s="5" t="s">
+      <c r="M34" s="2" t="s">
         <v>490</v>
       </c>
-      <c r="N34" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="O34" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="P34" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q34" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="S34" s="6">
+      <c r="N34" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="O34" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="P34" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q34" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="S34" s="3">
         <v>0.71430000000000005</v>
       </c>
-      <c r="T34" s="5" t="s">
+      <c r="T34" s="2" t="s">
         <v>540</v>
       </c>
-      <c r="U34" s="6">
+      <c r="U34" s="3">
         <v>0.55359999999999998</v>
       </c>
-      <c r="Z34" s="5" t="s">
+      <c r="Z34" s="2" t="s">
         <v>538</v>
       </c>
-      <c r="AC34" s="5" t="s">
+      <c r="AC34" s="2" t="s">
         <v>83</v>
       </c>
       <c r="AN34" s="5" t="s">
         <v>535</v>
       </c>
     </row>
-    <row r="35" spans="1:40" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="5" t="s">
+    <row r="35" spans="1:40" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="2" t="s">
         <v>495</v>
       </c>
-      <c r="B35" s="5">
+      <c r="B35" s="2">
         <v>2019</v>
       </c>
-      <c r="C35" s="5" t="s">
+      <c r="C35" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="D35" s="5" t="s">
+      <c r="D35" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="F35" s="5" t="e" vm="7">
+      <c r="F35" s="2" t="e" vm="7">
         <v>#VALUE!</v>
       </c>
-      <c r="G35" s="5" t="s">
+      <c r="G35" s="2" t="s">
         <v>537</v>
       </c>
-      <c r="H35" s="5" t="s">
+      <c r="H35" s="2" t="s">
         <v>497</v>
       </c>
-      <c r="I35" s="5" t="s">
+      <c r="I35" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="J35" s="5" t="s">
+      <c r="J35" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="K35" s="5" t="s">
+      <c r="K35" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="L35" s="5" t="s">
+      <c r="L35" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="M35" s="5" t="s">
+      <c r="M35" s="2" t="s">
         <v>490</v>
       </c>
-      <c r="N35" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="O35" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="P35" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q35" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="S35" s="6">
+      <c r="N35" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="O35" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="P35" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q35" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="S35" s="3">
         <v>0.63390000000000002</v>
       </c>
-      <c r="T35" s="5" t="s">
+      <c r="T35" s="2" t="s">
         <v>541</v>
       </c>
-      <c r="U35" s="6">
+      <c r="U35" s="3">
         <v>0.69640000000000002</v>
       </c>
-      <c r="Z35" s="5" t="s">
+      <c r="Z35" s="2" t="s">
         <v>539</v>
       </c>
-      <c r="AC35" s="5" t="s">
+      <c r="AC35" s="2" t="s">
         <v>83</v>
       </c>
       <c r="AN35" s="5" t="s">
         <v>535</v>
       </c>
     </row>
-    <row r="36" spans="1:40" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="5" t="s">
+    <row r="36" spans="1:40" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="2" t="s">
         <v>496</v>
       </c>
-      <c r="B36" s="5">
+      <c r="B36" s="2">
         <v>2020</v>
       </c>
-      <c r="C36" s="5" t="s">
+      <c r="C36" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D36" s="5" t="s">
+      <c r="D36" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="F36" s="5" t="e" vm="2">
+      <c r="F36" s="2" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
-      <c r="G36" s="5" t="s">
+      <c r="G36" s="2" t="s">
         <v>552</v>
       </c>
-      <c r="K36" s="5" t="s">
+      <c r="K36" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="L36" s="5" t="s">
+      <c r="L36" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="M36" s="5" t="s">
+      <c r="M36" s="2" t="s">
         <v>490</v>
       </c>
-      <c r="N36" s="5" t="s">
+      <c r="N36" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="O36" s="5" t="s">
+      <c r="O36" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="P36" s="5" t="s">
+      <c r="P36" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="Q36" s="5" t="s">
+      <c r="Q36" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="Z36" s="5" t="s">
+      <c r="Z36" s="2" t="s">
         <v>553</v>
       </c>
-      <c r="AC36" s="5" t="s">
+      <c r="AC36" s="2" t="s">
         <v>83</v>
       </c>
       <c r="AN36" s="5" t="s">
         <v>535</v>
       </c>
     </row>
-    <row r="37" spans="1:40" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="5" t="s">
+    <row r="37" spans="1:40" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="2" t="s">
         <v>496</v>
       </c>
-      <c r="B37" s="5">
+      <c r="B37" s="2">
         <v>2020</v>
       </c>
-      <c r="C37" s="5" t="s">
+      <c r="C37" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="D37" s="5" t="s">
+      <c r="D37" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="F37" s="5" t="e" vm="2">
+      <c r="F37" s="2" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
-      <c r="G37" s="5" t="s">
+      <c r="G37" s="2" t="s">
         <v>552</v>
       </c>
-      <c r="K37" s="5" t="s">
+      <c r="K37" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="L37" s="5" t="s">
+      <c r="L37" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="M37" s="5" t="s">
+      <c r="M37" s="2" t="s">
         <v>490</v>
       </c>
-      <c r="N37" s="5" t="s">
+      <c r="N37" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="O37" s="5" t="s">
+      <c r="O37" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="P37" s="5" t="s">
+      <c r="P37" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="Q37" s="5" t="s">
+      <c r="Q37" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="Z37" s="5" t="s">
+      <c r="Z37" s="2" t="s">
         <v>554</v>
       </c>
-      <c r="AC37" s="5" t="s">
+      <c r="AC37" s="2" t="s">
         <v>83</v>
       </c>
       <c r="AN37" s="5" t="s">
@@ -18579,7 +18626,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH33" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
+  <autoFilter ref="A1:BH19" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
